--- a/public/exports/19501817.xlsx
+++ b/public/exports/19501817.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports/19501817.xlsx
+++ b/public/exports/19501817.xlsx
@@ -11629,12 +11629,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
